--- a/DOCX/testcasexlsx.xlsx
+++ b/DOCX/testcasexlsx.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="164">
   <si>
     <t>TEST CASE – MULTI-FILE UPLOAD CLIENT/SERVER</t>
   </si>
@@ -374,151 +374,142 @@
     <t>CL_15</t>
   </si>
   <si>
-    <t>Kéo thả file</t>
-  </si>
-  <si>
-    <t>Kéo file vào vùng Drag &amp; Drop Files</t>
+    <t>Clear List</t>
+  </si>
+  <si>
+    <t>Đã có file trong danh sách</t>
+  </si>
+  <si>
+    <t>Nhấn Clear List</t>
   </si>
   <si>
     <t>CL_16</t>
   </si>
   <si>
-    <t>Clear List</t>
-  </si>
-  <si>
-    <t>Đã có file trong danh sách</t>
-  </si>
-  <si>
-    <t>Nhấn Clear List</t>
+    <t>Upload khi chưa kết nối</t>
+  </si>
+  <si>
+    <t>Có file trong danh sách, Client chưa Connected</t>
+  </si>
+  <si>
+    <t>Nhấn Upload</t>
   </si>
   <si>
     <t>CL_17</t>
   </si>
   <si>
-    <t>Upload khi chưa kết nối</t>
-  </si>
-  <si>
-    <t>Có file trong danh sách, Client chưa Connected</t>
-  </si>
-  <si>
-    <t>Nhấn Upload</t>
+    <t>Upload khi chưa chọn file</t>
+  </si>
+  <si>
+    <t>Client đã Connected, danh sách file trống</t>
   </si>
   <si>
     <t>CL_18</t>
   </si>
   <si>
-    <t>Upload khi chưa chọn file</t>
-  </si>
-  <si>
-    <t>Client đã Connected, danh sách file trống</t>
+    <t>Upload 1 file thành công</t>
+  </si>
+  <si>
+    <t>Client Connected, có 1 file</t>
   </si>
   <si>
     <t>CL_19</t>
   </si>
   <si>
-    <t>Upload 1 file thành công</t>
-  </si>
-  <si>
-    <t>Client Connected, có 1 file</t>
+    <t>Upload nhiều file thành công</t>
+  </si>
+  <si>
+    <t>Client Connected, có nhiều file</t>
   </si>
   <si>
     <t>CL_20</t>
   </si>
   <si>
-    <t>Upload nhiều file thành công</t>
-  </si>
-  <si>
-    <t>Client Connected, có nhiều file</t>
+    <t>Hiển thị tiến trình upload</t>
+  </si>
+  <si>
+    <t>Đang upload file</t>
+  </si>
+  <si>
+    <t>Quan sát cột Tiến trình</t>
   </si>
   <si>
     <t>CL_21</t>
   </si>
   <si>
-    <t>Hiển thị tiến trình upload</t>
-  </si>
-  <si>
-    <t>Đang upload file</t>
-  </si>
-  <si>
-    <t>Quan sát cột Tiến trình</t>
+    <t>Pause upload</t>
+  </si>
+  <si>
+    <t>Nhấn Pause</t>
   </si>
   <si>
     <t>CL_22</t>
   </si>
   <si>
-    <t>Pause upload</t>
-  </si>
-  <si>
-    <t>Nhấn Pause</t>
+    <t>Resume upload</t>
+  </si>
+  <si>
+    <t>File đang Paused</t>
+  </si>
+  <si>
+    <t>Nhấn Resume</t>
   </si>
   <si>
     <t>CL_23</t>
   </si>
   <si>
-    <t>Resume upload</t>
-  </si>
-  <si>
-    <t>File đang Paused</t>
-  </si>
-  <si>
-    <t>Nhấn Resume</t>
+    <t>Disconnect khi đang upload</t>
   </si>
   <si>
     <t>CL_24</t>
   </si>
   <si>
-    <t>Disconnect khi đang upload</t>
+    <t>Upload file trùng tên</t>
+  </si>
+  <si>
+    <t>Server đã có file cùng tên</t>
+  </si>
+  <si>
+    <t>Upload lại file cùng tên</t>
   </si>
   <si>
     <t>CL_25</t>
   </si>
   <si>
-    <t>Upload file trùng tên</t>
-  </si>
-  <si>
-    <t>Server đã có file cùng tên</t>
-  </si>
-  <si>
-    <t>Upload lại file cùng tên</t>
+    <t>Upload file dung lượng 0 KB</t>
+  </si>
+  <si>
+    <t>Chọn file rỗng</t>
   </si>
   <si>
     <t>CL_26</t>
   </si>
   <si>
-    <t>Upload file dung lượng 0 KB</t>
-  </si>
-  <si>
-    <t>Chọn file rỗng</t>
+    <t>Upload file lớn</t>
+  </si>
+  <si>
+    <t>Chọn file dung lượng lớn</t>
   </si>
   <si>
     <t>CL_27</t>
   </si>
   <si>
-    <t>Upload file lớn</t>
-  </si>
-  <si>
-    <t>Chọn file dung lượng lớn</t>
+    <t>Upload file có tên tiếng Việt</t>
+  </si>
+  <si>
+    <t>Chọn file tên báo cáo.docx</t>
   </si>
   <si>
     <t>CL_28</t>
   </si>
   <si>
-    <t>Upload file có tên tiếng Việt</t>
-  </si>
-  <si>
-    <t>Chọn file tên báo cáo.docx</t>
+    <t>Upload file có ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>Chọn file tên test @#$%.txt</t>
   </si>
   <si>
     <t>CL_29</t>
-  </si>
-  <si>
-    <t>Upload file có ký tự đặc biệt</t>
-  </si>
-  <si>
-    <t>Chọn file tên test @#$%.txt</t>
-  </si>
-  <si>
-    <t>CL_30</t>
   </si>
   <si>
     <t>Đóng Client khi đang kết nối</t>
@@ -2233,44 +2224,44 @@
         <v>115</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E35" s="4"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" ht="28.8" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E36" s="4"/>
     </row>
     <row r="37" ht="28.8" spans="1:5">
       <c r="A37" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="E37" s="4"/>
     </row>
-    <row r="38" ht="28.8" spans="1:5">
+    <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
         <v>125</v>
       </c>
@@ -2281,7 +2272,7 @@
         <v>127</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E38" s="4"/>
     </row>
@@ -2296,7 +2287,7 @@
         <v>130</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E39" s="4"/>
     </row>
@@ -2311,19 +2302,19 @@
         <v>133</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E40" s="4"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>137</v>
@@ -2338,55 +2329,55 @@
         <v>139</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E42" s="4"/>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="D44" s="5" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="E44" s="4"/>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="E45" s="4"/>
     </row>
@@ -2401,7 +2392,7 @@
         <v>153</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E46" s="4"/>
     </row>
@@ -2416,7 +2407,7 @@
         <v>156</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E47" s="4"/>
     </row>
@@ -2430,8 +2421,8 @@
       <c r="C48" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>124</v>
+      <c r="D48" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="E48" s="4"/>
     </row>
@@ -2446,23 +2437,12 @@
         <v>162</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="E49" s="4"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>166</v>
-      </c>
+      <c r="A50" s="3"/>
       <c r="E50" s="4"/>
     </row>
     <row r="51" spans="1:5">

--- a/DOCX/testcasexlsx.xlsx
+++ b/DOCX/testcasexlsx.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="256">
   <si>
     <t>TEST CASE – MULTI-FILE UPLOAD CLIENT/SERVER</t>
   </si>
@@ -53,6 +53,9 @@
     <t>Minh chứng</t>
   </si>
   <si>
+    <t>Minh chứng bổ sung</t>
+  </si>
+  <si>
     <t>SV_01</t>
   </si>
   <si>
@@ -344,175 +347,214 @@
     <t>Giao diện client hiện đầy đủ</t>
   </si>
   <si>
+    <t>Envidence\Client\CL_01.png</t>
+  </si>
+  <si>
     <t>CL_02</t>
   </si>
   <si>
-    <t>Trạng thái ban đầu của Client</t>
-  </si>
-  <si>
-    <t>Vừa mở Client</t>
-  </si>
-  <si>
-    <t>Quan sát giao diện</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Giao diện hiển thị đầy đủ các nút chức năng </t>
+    <t>Nhập Server IP hợp lệ</t>
+  </si>
+  <si>
+    <t>Client đang Disconnected</t>
+  </si>
+  <si>
+    <t>Nhập IP Server, ví dụ 191.158.1.230</t>
+  </si>
+  <si>
+    <t>IP được điền chính xác vào ô Server/Host</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_02.png</t>
   </si>
   <si>
     <t>CL_03</t>
   </si>
   <si>
-    <t>Nhập Server IP hợp lệ</t>
-  </si>
-  <si>
-    <t>Client đang Disconnected</t>
-  </si>
-  <si>
-    <t>Nhập IP Server, ví dụ 191.158.1.230</t>
-  </si>
-  <si>
-    <t>IP được điền chính xác vào ô Server/Host</t>
+    <t>Nhập Port hợp lệ</t>
+  </si>
+  <si>
+    <t>Nhập port, ví dụ 9000</t>
+  </si>
+  <si>
+    <t>Port được điền vào ô Port thành công</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_03.png</t>
   </si>
   <si>
     <t>CL_04</t>
   </si>
   <si>
-    <t>Nhập Port hợp lệ</t>
-  </si>
-  <si>
-    <t>Nhập port, ví dụ 9000</t>
-  </si>
-  <si>
-    <t>Port được điền vào ô Port thành công</t>
+    <t>Connect thành công</t>
+  </si>
+  <si>
+    <t>Server đang Online, IP/Port đúng</t>
+  </si>
+  <si>
+    <t>Nhấn Connect</t>
+  </si>
+  <si>
+    <t>Kết nối server thành công, hiện Connected</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_04.png</t>
   </si>
   <si>
     <t>CL_05</t>
   </si>
   <si>
-    <t>Connect thành công</t>
-  </si>
-  <si>
-    <t>Server đang Online, IP/Port đúng</t>
-  </si>
-  <si>
-    <t>Nhấn Connect</t>
-  </si>
-  <si>
-    <t>Kết nối server thành công, hiện Connected</t>
+    <t>Connect khi chưa nhập IP</t>
+  </si>
+  <si>
+    <t>Ô IP để trống</t>
+  </si>
+  <si>
+    <t>Thông báo Vui lòng nhập Sever IP/Host</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_05.png</t>
   </si>
   <si>
     <t>CL_06</t>
   </si>
   <si>
-    <t>Connect khi chưa nhập IP</t>
-  </si>
-  <si>
-    <t>Ô IP để trống</t>
-  </si>
-  <si>
-    <t>Yêu cầu nhập IP, không kết nối được</t>
+    <t>Connect khi chưa nhập Port</t>
+  </si>
+  <si>
+    <t>Thông báo Port chỉ được nhập số nguyên từ 0 đến 65535</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_06.png</t>
   </si>
   <si>
     <t>CL_07</t>
   </si>
   <si>
-    <t>Connect khi chưa nhập Port</t>
-  </si>
-  <si>
-    <t>Thông báo lỗi Port</t>
+    <t>Connect sai IP</t>
+  </si>
+  <si>
+    <t>Nhập IP không tồn tại</t>
+  </si>
+  <si>
+    <t>Thông báo Sever chưa bật hoặc nhập sai IP/Port</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_07.png</t>
   </si>
   <si>
     <t>CL_08</t>
   </si>
   <si>
-    <t>Connect sai IP</t>
-  </si>
-  <si>
-    <t>Nhập IP không tồn tại</t>
-  </si>
-  <si>
-    <t>Thông báo lỗi IP/Port</t>
+    <t>Connect sai Port</t>
+  </si>
+  <si>
+    <t>Server chạy port 9000, Client nhập 8000</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_08.png</t>
   </si>
   <si>
     <t>CL_09</t>
   </si>
   <si>
-    <t>Connect sai Port</t>
-  </si>
-  <si>
-    <t>Server chạy port 9000, Client nhập 8000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thông báo lỗi </t>
+    <t>Connect khi Server chưa Start</t>
+  </si>
+  <si>
+    <t>Server Offline</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_09.png</t>
   </si>
   <si>
     <t>CL_10</t>
   </si>
   <si>
-    <t>Connect khi Server chưa Start</t>
-  </si>
-  <si>
-    <t>Server Offline</t>
-  </si>
-  <si>
-    <t>Thông báo lỗi</t>
+    <t>Không cho Connect lần 2</t>
+  </si>
+  <si>
+    <t>Client đã Connected</t>
+  </si>
+  <si>
+    <t>Nhấn Connect lần nữa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hệ thống không cho nhấn connect nữa </t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_10.png</t>
   </si>
   <si>
     <t>CL_11</t>
   </si>
   <si>
-    <t>Không cho Connect lần 2</t>
-  </si>
-  <si>
-    <t>Client đã Connected</t>
-  </si>
-  <si>
-    <t>Nhấn Connect lần nữa</t>
-  </si>
-  <si>
-    <t>Hệ thống từ chối kết nối</t>
+    <t>Disconnect thành công</t>
+  </si>
+  <si>
+    <t>Client đang Connected</t>
+  </si>
+  <si>
+    <t>Nhấn Disconnect</t>
+  </si>
+  <si>
+    <t>Chuyển sang Disconnected, ngắt kết nối Server</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_11.png</t>
   </si>
   <si>
     <t>CL_12</t>
   </si>
   <si>
-    <t>Disconnect thành công</t>
-  </si>
-  <si>
-    <t>Client đang Connected</t>
-  </si>
-  <si>
-    <t>Nhấn Disconnect</t>
-  </si>
-  <si>
-    <t>Chuyển sang Disconnected, ngắt kết nối Server</t>
+    <t>Chọn 1 file</t>
+  </si>
+  <si>
+    <t>Client đang mở</t>
+  </si>
+  <si>
+    <t>Nhấn Select Files, chọn 1 file</t>
+  </si>
+  <si>
+    <t>Hộp thoại chọn file xuất hiện, chọn xong file hiển thị trong danh sách chờ upload</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_12.1.png</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_12.2.png</t>
   </si>
   <si>
     <t>CL_13</t>
   </si>
   <si>
-    <t>Chọn 1 file</t>
-  </si>
-  <si>
-    <t>Client đang mở</t>
-  </si>
-  <si>
-    <t>Nhấn Select Files, chọn 1 file</t>
-  </si>
-  <si>
-    <t>Hộp thoại chọn file xuất hiện, chọn xong file hiển thị trong danh sách chờ upload</t>
+    <t>Chọn nhiều file</t>
+  </si>
+  <si>
+    <t>Nhấn Select Files, chọn nhiều file</t>
+  </si>
+  <si>
+    <t>Tất cả file được chọn hiển thị đầy đủ trong danh sách file chờ upload</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_13.1.png</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_13.2.png</t>
   </si>
   <si>
     <t>CL_14</t>
   </si>
   <si>
-    <t>Chọn nhiều file</t>
-  </si>
-  <si>
-    <t>Nhấn Select Files, chọn nhiều file</t>
-  </si>
-  <si>
-    <t>Tất cả file được chọn hiển thị đầy đủ trong danh sách file chờ upload</t>
+    <t>Kéo file thả vào ô thả file</t>
+  </si>
+  <si>
+    <t>Kéo file vào ô thả file</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_14.1.png</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_14.2.png</t>
   </si>
   <si>
     <t>CL_15</t>
@@ -530,6 +572,9 @@
     <t>Danh sách file bị xóa sạch</t>
   </si>
   <si>
+    <t>Envidence\Client\CL_15.png</t>
+  </si>
+  <si>
     <t>CL_16</t>
   </si>
   <si>
@@ -545,6 +590,9 @@
     <t>Không thực hiện upload do chưa kết nối</t>
   </si>
   <si>
+    <t>Envidence\Client\CL_16.png</t>
+  </si>
+  <si>
     <t>CL_17</t>
   </si>
   <si>
@@ -554,7 +602,10 @@
     <t>Client đã Connected, danh sách file trống</t>
   </si>
   <si>
-    <t>Hệ thống không thực hiện gì</t>
+    <t>Hệ thống không thể update khi chưa chọn file</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_17.png</t>
   </si>
   <si>
     <t>CL_18</t>
@@ -569,6 +620,9 @@
     <t>Thanh tiến trình chạy, file được truyền sang server</t>
   </si>
   <si>
+    <t>Envidence\Client\CL_18.png</t>
+  </si>
+  <si>
     <t>CL_19</t>
   </si>
   <si>
@@ -581,6 +635,9 @@
     <t>Tất cả file lần lượt được được hiển thị</t>
   </si>
   <si>
+    <t>Envidence\Client\CL_19.png</t>
+  </si>
+  <si>
     <t>CL_20</t>
   </si>
   <si>
@@ -596,6 +653,9 @@
     <t>Hiển thị từ 0% đến 100%</t>
   </si>
   <si>
+    <t>Envidence\Client\CL_20.png</t>
+  </si>
+  <si>
     <t>CL_21</t>
   </si>
   <si>
@@ -608,6 +668,9 @@
     <t>Quá trình upload tạm dừng</t>
   </si>
   <si>
+    <t>Envidence\Client\CL_21.png</t>
+  </si>
+  <si>
     <t>CL_22</t>
   </si>
   <si>
@@ -623,6 +686,9 @@
     <t>Quá trình upload tiếp tục chạy</t>
   </si>
   <si>
+    <t>Envidence\Client\CL_22.png</t>
+  </si>
+  <si>
     <t>CL_23</t>
   </si>
   <si>
@@ -632,6 +698,9 @@
     <t>Ngắt kết nối server, quá trình upload tạm dừng</t>
   </si>
   <si>
+    <t>Envidence\Client\CL_23.png</t>
+  </si>
+  <si>
     <t>CL_24</t>
   </si>
   <si>
@@ -644,7 +713,10 @@
     <t>Upload lại file cùng tên</t>
   </si>
   <si>
-    <t xml:space="preserve">Hệ thống không thực hiện lấy file đã trùng </t>
+    <t>Hệ thống sẽ đổi tên file mới để không bị ở nơi lưu trữ sever</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_24.png</t>
   </si>
   <si>
     <t>CL_25</t>
@@ -656,7 +728,10 @@
     <t>Chọn file rỗng</t>
   </si>
   <si>
-    <t>Hệ thống bỏ qua file rỗng</t>
+    <t>Hệ thống upload bình thường</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_25.png</t>
   </si>
   <si>
     <t>CL_26</t>
@@ -671,6 +746,9 @@
     <t>Hệ thống vẫn xử lý được</t>
   </si>
   <si>
+    <t>Envidence\Client\CL_26.png</t>
+  </si>
+  <si>
     <t>CL_27</t>
   </si>
   <si>
@@ -683,6 +761,9 @@
     <t>File được upload thành công, vẫn giữ nguyên tên</t>
   </si>
   <si>
+    <t>Envidence\Client\CL_27.png</t>
+  </si>
+  <si>
     <t>CL_28</t>
   </si>
   <si>
@@ -695,6 +776,9 @@
     <t>File được upload thành công, không lỗi các ký tự đặc biệt</t>
   </si>
   <si>
+    <t>Envidence\Client\CL_28.png</t>
+  </si>
+  <si>
     <t>CL_29</t>
   </si>
   <si>
@@ -708,6 +792,9 @@
   </si>
   <si>
     <t>Ngắt kết nối an toàn với server không gây lỗi</t>
+  </si>
+  <si>
+    <t>Envidence\Client\CL_29.png</t>
   </si>
 </sst>
 </file>
@@ -720,33 +807,13 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
@@ -782,23 +849,31 @@
       <charset val="163"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="14"/>
       <color rgb="FF081B3A"/>
       <name val="Times New Roman"/>
       <charset val="163"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1275,137 +1350,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1415,13 +1490,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1430,34 +1499,55 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="6" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1985,1153 +2075,1267 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G62"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:H62"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="41.5555555555556" customWidth="1"/>
     <col min="3" max="3" width="27.8888888888889" customWidth="1"/>
     <col min="4" max="4" width="37.7777777777778" customWidth="1"/>
     <col min="5" max="5" width="32.8888888888889" customWidth="1"/>
     <col min="6" max="6" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.2222222222222" customWidth="1"/>
+    <col min="7" max="7" width="28.7222222222222" customWidth="1"/>
+    <col min="8" max="8" width="35.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:7">
+    <row r="1" ht="18" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" ht="17.4" spans="1:7">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" ht="17.4" spans="1:8">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" ht="36" spans="1:7">
-      <c r="A3" s="7" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7" t="s">
+    </row>
+    <row r="3" ht="36" spans="1:8">
+      <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" ht="36" spans="1:7">
-      <c r="A4" s="7" t="s">
+      <c r="F3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" ht="36" spans="1:8">
+      <c r="A4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="36" spans="1:7">
-      <c r="A5" s="7" t="s">
+      <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="F4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" ht="36" spans="1:8">
+      <c r="A5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="36" spans="1:7">
-      <c r="A6" s="7" t="s">
+      <c r="E5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="F5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" ht="36" spans="1:8">
+      <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" ht="54" spans="1:7">
-      <c r="A7" s="7" t="s">
+      <c r="D6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="F6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" ht="54" spans="1:8">
+      <c r="A7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="B7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="C7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" ht="36" spans="1:7">
-      <c r="A8" s="7" t="s">
+      <c r="E7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="F7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" ht="36" spans="1:8">
+      <c r="A8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="C8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" ht="54" spans="1:7">
-      <c r="A9" s="7" t="s">
+      <c r="E8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="F8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" ht="54" spans="1:8">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="C9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" ht="36" spans="1:7">
-      <c r="A10" s="7" t="s">
+      <c r="E9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="F9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" ht="36" spans="1:8">
+      <c r="A10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="D10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1" spans="1:7">
-      <c r="A11" s="7" t="s">
+      <c r="E10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="F10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" ht="45" customHeight="1" spans="1:8">
+      <c r="A11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="C11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" ht="36" spans="1:7">
-      <c r="A12" s="7" t="s">
+      <c r="E11" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="F11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" ht="36" spans="1:8">
+      <c r="A12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="C12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" ht="36" spans="1:7">
-      <c r="A13" s="7" t="s">
+      <c r="E12" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="F12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" ht="36" spans="1:8">
+      <c r="A13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="D13" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" ht="66.6" customHeight="1" spans="1:7">
-      <c r="A14" s="7" t="s">
+      <c r="E13" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="F13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" ht="66.6" customHeight="1" spans="1:8">
+      <c r="A14" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="C14" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="D14" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" ht="54" spans="1:7">
-      <c r="A15" s="7" t="s">
+      <c r="E14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="F14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" ht="54" spans="1:8">
+      <c r="A15" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="B15" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="C15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" ht="36" spans="1:7">
-      <c r="A16" s="7" t="s">
+      <c r="E15" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="F15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" ht="36" spans="1:8">
+      <c r="A16" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="B16" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="C16" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" ht="36" spans="1:7">
-      <c r="A17" s="7" t="s">
+      <c r="E16" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="F16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" ht="36" spans="1:8">
+      <c r="A17" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="8" t="s">
+      <c r="B17" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="C17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" ht="36" spans="1:7">
-      <c r="A18" s="7" t="s">
+      <c r="E17" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="F17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" ht="36" spans="1:8">
+      <c r="A18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="B18" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="D18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" ht="54" spans="1:7">
-      <c r="A19" s="7" t="s">
+      <c r="E18" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="F18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" ht="54" spans="1:8">
+      <c r="A19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="7" t="s">
+      <c r="C19" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" ht="18" spans="1:7">
-      <c r="A20" s="7" t="s">
+      <c r="D19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="F19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" ht="18" spans="1:8">
+      <c r="A20" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="B20" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="C20" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="D20" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" ht="54" spans="1:7">
-      <c r="A21" s="7" t="s">
+      <c r="E20" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="F20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" ht="54" spans="1:8">
+      <c r="A21" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="C21" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="D21" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" ht="54" spans="1:7">
-      <c r="A22" s="7" t="s">
+      <c r="E21" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="F21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" ht="54" spans="1:8">
+      <c r="A22" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="C22" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="D22" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="F22" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" ht="18" spans="1:7">
-      <c r="A23" s="7" t="s">
+      <c r="E22" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="F22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" ht="18" spans="1:8">
+      <c r="A23" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="B23" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="C23" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="D23" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="14"/>
-    </row>
-    <row r="24" ht="18" spans="1:7">
-      <c r="A24" s="7" t="s">
+      <c r="E23" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="F23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" ht="36" spans="1:8">
+      <c r="A24" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="B24" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="C24" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="14"/>
-    </row>
-    <row r="25" ht="36" spans="1:7">
-      <c r="A25" s="7" t="s">
+      <c r="D24" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="E24" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="F24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" ht="36" spans="1:8">
+      <c r="A25" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="B25" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="14"/>
-    </row>
-    <row r="26" ht="36" spans="1:7">
-      <c r="A26" s="7" t="s">
+      <c r="C25" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="E25" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" s="7" t="s">
+      <c r="F25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" ht="36" spans="1:8">
+      <c r="A26" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="14"/>
-    </row>
-    <row r="27" ht="30" customHeight="1" spans="1:7">
-      <c r="A27" s="7" t="s">
+      <c r="B26" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="C26" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="D26" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="E26" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="F26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="F27" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="14"/>
-    </row>
-    <row r="28" ht="36" spans="1:7">
-      <c r="A28" s="7" t="s">
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:8">
+      <c r="A27" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B27" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C27" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E28" s="7" t="s">
+      <c r="D27" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="14"/>
-    </row>
-    <row r="29" ht="18" spans="1:7">
-      <c r="A29" s="7" t="s">
+      <c r="F27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" ht="36" spans="1:8">
+      <c r="A28" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" s="7" t="s">
+      <c r="B28" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="14"/>
-    </row>
-    <row r="30" ht="18" spans="1:7">
-      <c r="A30" s="7" t="s">
+      <c r="C28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="F28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" ht="36" spans="1:8">
+      <c r="A29" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E30" s="7" t="s">
+      <c r="B29" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="14"/>
-    </row>
-    <row r="31" ht="36" spans="1:7">
-      <c r="A31" s="7" t="s">
+      <c r="C29" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="D29" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="F29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E31" s="7" t="s">
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" ht="36" spans="1:8">
+      <c r="A30" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="14"/>
-    </row>
-    <row r="32" ht="18" spans="1:7">
-      <c r="A32" s="7" t="s">
+      <c r="B30" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="C30" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="D30" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E32" s="7" t="s">
+      <c r="H30" s="8"/>
+    </row>
+    <row r="31" ht="36" spans="1:8">
+      <c r="A31" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="14"/>
-    </row>
-    <row r="33" ht="18" spans="1:7">
-      <c r="A33" s="7" t="s">
+      <c r="B31" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="C31" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D31" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="H31" s="8"/>
+    </row>
+    <row r="32" ht="36" spans="1:8">
+      <c r="A32" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="B32" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="14"/>
-    </row>
-    <row r="34" ht="36" spans="1:7">
-      <c r="A34" s="7" t="s">
+      <c r="C32" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="D32" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="E32" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="F32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="H32" s="8"/>
+    </row>
+    <row r="33" ht="36" spans="1:8">
+      <c r="A33" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="F34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="14"/>
-    </row>
-    <row r="35" ht="54" spans="1:7">
-      <c r="A35" s="7" t="s">
+      <c r="B33" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="C33" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="D33" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="E33" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="F33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="14"/>
-    </row>
-    <row r="36" ht="54" spans="1:7">
-      <c r="A36" s="7" t="s">
+      <c r="H33" s="8"/>
+    </row>
+    <row r="34" ht="54" spans="1:8">
+      <c r="A34" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B34" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C34" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" ht="54" spans="1:8">
+      <c r="A35" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36" ht="18" spans="1:8">
+      <c r="A36" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" s="17"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37" ht="36" spans="1:8">
+      <c r="A37" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="H37" s="8"/>
+    </row>
+    <row r="38" ht="36" spans="1:8">
+      <c r="A38" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" ht="36" spans="1:8">
+      <c r="A39" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H39" s="8"/>
+    </row>
+    <row r="40" ht="36" spans="1:8">
+      <c r="A40" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="H40" s="8"/>
+    </row>
+    <row r="41" ht="36" spans="1:8">
+      <c r="A41" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="H41" s="8"/>
+    </row>
+    <row r="42" ht="18" spans="1:8">
+      <c r="A42" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" ht="18" spans="1:8">
+      <c r="A43" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="H43" s="8"/>
+    </row>
+    <row r="44" ht="18" spans="1:8">
+      <c r="A44" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="H44" s="8"/>
+    </row>
+    <row r="45" ht="36" spans="1:8">
+      <c r="A45" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="14"/>
-    </row>
-    <row r="37" ht="36" spans="1:7">
-      <c r="A37" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="14"/>
-    </row>
-    <row r="38" ht="36" spans="1:7">
-      <c r="A38" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="14"/>
-    </row>
-    <row r="39" ht="36" spans="1:7">
-      <c r="A39" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="14"/>
-    </row>
-    <row r="40" ht="36" spans="1:7">
-      <c r="A40" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="14"/>
-    </row>
-    <row r="41" ht="36" spans="1:7">
-      <c r="A41" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="14"/>
-    </row>
-    <row r="42" ht="18" spans="1:7">
-      <c r="A42" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B42" s="7" t="s">
+      <c r="E45" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="H45" s="8"/>
+    </row>
+    <row r="46" ht="36" spans="1:8">
+      <c r="A46" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="H46" s="8"/>
+    </row>
+    <row r="47" ht="18" spans="1:8">
+      <c r="A47" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="14"/>
-    </row>
-    <row r="43" ht="18" spans="1:7">
-      <c r="A43" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="14"/>
-    </row>
-    <row r="44" ht="18" spans="1:7">
-      <c r="A44" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="14"/>
-    </row>
-    <row r="45" ht="36" spans="1:7">
-      <c r="A45" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="14"/>
-    </row>
-    <row r="46" ht="36" spans="1:7">
-      <c r="A46" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="14"/>
-    </row>
-    <row r="47" ht="18" spans="1:7">
-      <c r="A47" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="14"/>
-    </row>
-    <row r="48" ht="18" spans="1:7">
-      <c r="A48" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="14"/>
-    </row>
-    <row r="49" ht="36" spans="1:7">
-      <c r="A49" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="14"/>
-    </row>
-    <row r="50" ht="36" spans="1:7">
-      <c r="A50" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="14"/>
-    </row>
-    <row r="51" ht="36" spans="1:7">
-      <c r="A51" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="14"/>
-    </row>
-    <row r="52" ht="15.6" spans="1:7">
-      <c r="A52" s="16"/>
-      <c r="F52" s="17"/>
-    </row>
-    <row r="53" ht="15.6" spans="1:7">
-      <c r="F53" s="17"/>
-    </row>
-    <row r="54" ht="15.6" spans="1:7">
-      <c r="F54" s="17"/>
-    </row>
-    <row r="55" ht="15.6" spans="1:7">
-      <c r="F55" s="17"/>
-    </row>
-    <row r="56" ht="15.6" spans="1:7">
-      <c r="F56" s="17"/>
-    </row>
-    <row r="57" ht="15.6" spans="1:7">
-      <c r="F57" s="17"/>
-    </row>
-    <row r="58" ht="15.6" spans="1:7">
-      <c r="F58" s="17"/>
-    </row>
-    <row r="59" ht="15.6" spans="1:7">
-      <c r="F59" s="17"/>
-    </row>
-    <row r="60" ht="15.6" spans="1:7">
-      <c r="F60" s="17"/>
-    </row>
-    <row r="61" ht="15.6" spans="1:7">
-      <c r="F61" s="17"/>
-    </row>
-    <row r="62" ht="15.6" spans="1:7">
-      <c r="F62" s="17"/>
+      <c r="E47" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="H47" s="8"/>
+    </row>
+    <row r="48" ht="18" spans="1:8">
+      <c r="A48" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="H48" s="8"/>
+    </row>
+    <row r="49" ht="36" spans="1:8">
+      <c r="A49" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" ht="36" spans="1:8">
+      <c r="A50" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="H50" s="8"/>
+    </row>
+    <row r="51" ht="36" spans="1:8">
+      <c r="A51" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H51" s="8"/>
+    </row>
+    <row r="52" ht="15.6" spans="1:8">
+      <c r="A52" s="20"/>
+      <c r="B52" s="21"/>
+      <c r="F52" s="22"/>
+    </row>
+    <row r="53" ht="15.6" spans="1:8">
+      <c r="F53" s="22"/>
+    </row>
+    <row r="54" ht="15.6" spans="1:8">
+      <c r="F54" s="22"/>
+    </row>
+    <row r="55" ht="15.6" spans="1:8">
+      <c r="F55" s="22"/>
+    </row>
+    <row r="56" ht="15.6" spans="1:8">
+      <c r="F56" s="22"/>
+    </row>
+    <row r="57" ht="15.6" spans="1:8">
+      <c r="F57" s="22"/>
+    </row>
+    <row r="58" ht="15.6" spans="1:8">
+      <c r="F58" s="22"/>
+    </row>
+    <row r="59" ht="15.6" spans="1:8">
+      <c r="F59" s="22"/>
+    </row>
+    <row r="60" ht="15.6" spans="1:8">
+      <c r="F60" s="22"/>
+    </row>
+    <row r="61" ht="15.6" spans="1:8">
+      <c r="F61" s="22"/>
+    </row>
+    <row r="62" ht="15.6" spans="1:8">
+      <c r="F62" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3158,6 +3362,38 @@
     <hyperlink ref="G20" r:id="rId18" display="Xem ảnh"/>
     <hyperlink ref="G21" r:id="rId19" display="Xem ảnh"/>
     <hyperlink ref="G22" r:id="rId20" display="Xem ảnh"/>
+    <hyperlink ref="G23" r:id="rId21" display="Envidence\Client\CL_01.png"/>
+    <hyperlink ref="G24" r:id="rId22" display="Envidence\Client\CL_02.png"/>
+    <hyperlink ref="G25" r:id="rId23" display="Envidence\Client\CL_03.png"/>
+    <hyperlink ref="G26" r:id="rId24" display="Envidence\Client\CL_04.png"/>
+    <hyperlink ref="G27" r:id="rId25" display="Envidence\Client\CL_05.png"/>
+    <hyperlink ref="G28" r:id="rId26" display="Envidence\Client\CL_06.png"/>
+    <hyperlink ref="G29" r:id="rId27" display="Envidence\Client\CL_07.png"/>
+    <hyperlink ref="G30" r:id="rId28" display="Envidence\Client\CL_08.png"/>
+    <hyperlink ref="G31" r:id="rId29" display="Envidence\Client\CL_09.png"/>
+    <hyperlink ref="G32" r:id="rId30" display="Envidence\Client\CL_10.png"/>
+    <hyperlink ref="G33" r:id="rId31" display="Envidence\Client\CL_11.png"/>
+    <hyperlink ref="G34" r:id="rId32" display="Envidence\Client\CL_12.1.png"/>
+    <hyperlink ref="H34" r:id="rId33" display="Envidence\Client\CL_12.2.png"/>
+    <hyperlink ref="G35" r:id="rId34" display="Envidence\Client\CL_13.1.png"/>
+    <hyperlink ref="H35" r:id="rId35" display="Envidence\Client\CL_13.2.png"/>
+    <hyperlink ref="G36" r:id="rId36" display="Envidence\Client\CL_14.1.png"/>
+    <hyperlink ref="H36" r:id="rId37" display="Envidence\Client\CL_14.2.png"/>
+    <hyperlink ref="G37" r:id="rId38" display="Envidence\Client\CL_15.png"/>
+    <hyperlink ref="G38" r:id="rId39" display="Envidence\Client\CL_16.png"/>
+    <hyperlink ref="G39" r:id="rId40" display="Envidence\Client\CL_17.png"/>
+    <hyperlink ref="G40" r:id="rId41" display="Envidence\Client\CL_18.png"/>
+    <hyperlink ref="G41" r:id="rId42" display="Envidence\Client\CL_19.png"/>
+    <hyperlink ref="G42" r:id="rId43" display="Envidence\Client\CL_20.png"/>
+    <hyperlink ref="G43" r:id="rId44" display="Envidence\Client\CL_21.png"/>
+    <hyperlink ref="G44" r:id="rId45" display="Envidence\Client\CL_22.png"/>
+    <hyperlink ref="G45" r:id="rId46" display="Envidence\Client\CL_23.png"/>
+    <hyperlink ref="G46" r:id="rId47" display="Envidence\Client\CL_24.png"/>
+    <hyperlink ref="G47" r:id="rId48" display="Envidence\Client\CL_25.png"/>
+    <hyperlink ref="G48" r:id="rId49" display="Envidence\Client\CL_26.png"/>
+    <hyperlink ref="G49" r:id="rId50" display="Envidence\Client\CL_27.png"/>
+    <hyperlink ref="G50" r:id="rId51" display="Envidence\Client\CL_28.png"/>
+    <hyperlink ref="G51" r:id="rId52" display="Envidence\Client\CL_29.png"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
